--- a/FellowshipChampionships/FellowshipChampionships.xlsx
+++ b/FellowshipChampionships/FellowshipChampionships.xlsx
@@ -1,80 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gleesonm/projects/FellowshipRaceSeries/FellowshipChampionships/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE62CE80-8172-8441-9F06-4EE7BA683425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="GC" sheetId="1" r:id="rId1"/>
-    <sheet name="e_gap" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GC" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="e_gap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team GC" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprints" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KQOM" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Round 1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Round 2" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Round 3" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Round 4" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Round 5" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="10">
-  <si>
-    <t>zwift_id</t>
-  </si>
-  <si>
-    <t>pen</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>age</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>team_name</t>
-  </si>
-  <si>
-    <t>total_time</t>
-  </si>
-  <si>
-    <t>time_offset</t>
-  </si>
-  <si>
-    <t>races</t>
-  </si>
-  <si>
-    <t>e_gap</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -89,43 +55,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -413,37 +429,624 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>zwift_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>pen</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>total_time</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>time_offset</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>races</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7965630</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mas</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Dexter Nguyen [Fellowship]</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>58:06.300</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8205262</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Jnr</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Seung-ah Lee&amp;#129430;</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>55:30.722</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8076817</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mas</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ben Fryett (Fellowship)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>55:48.842</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>18.120</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8311695</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mas</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Kyle Mueller (Fellowship)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>56:09.419</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>38.697</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1039349</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>60+</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Joey Austerman</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>56:24.467</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>53.745</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8029063</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mas</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Marlon Garcia</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>56:39.612</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>01:08.890</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8344285</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Vet</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Wayne Giles</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>56:42.739</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>01:12.017</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6683427</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mas</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Evan Davis [Fellowship]</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>58:35.367</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>03:04.645</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8145883</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Vet</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matthew Carter (Fellowship) </t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>59:17.908</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>03:47.186</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7742231</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Snr</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Carter Costner [Fellowship]</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>59:55.579</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6931981</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Mas</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Zachery Reinke</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>01:00:48.081</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>52.502</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4148536</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Vet</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Corey K</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>01:02:02.811</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>02:07.232</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -451,38 +1054,2468 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>zwift_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>pen</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>e_gap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>total_time</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>races completed</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>e_gap1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7965630</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mas</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Dexter Nguyen [Fellowship]</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>58:06.300</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8205262</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Jnr</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Seung-ah Lee&amp;#129430;</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>55:30.722</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8076817</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mas</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ben Fryett (Fellowship)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>18.120</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>55:48.842</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>18.120</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8311695</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mas</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Kyle Mueller (Fellowship)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>38.697</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>56:09.419</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>38.697</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1039349</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>60+</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Joey Austerman</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>53.745</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>56:24.467</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>53.745</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8029063</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mas</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Marlon Garcia</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>01:08.890</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>56:39.612</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>01:08.890</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8344285</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Vet</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Wayne Giles</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>01:12.017</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>56:42.739</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>01:12.017</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6683427</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mas</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Evan Davis [Fellowship]</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>03:04.645</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>58:35.367</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>03:04.645</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8145883</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Vet</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matthew Carter (Fellowship) </t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>03:47.186</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>59:17.908</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>03:47.186</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7742231</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Snr</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Carter Costner [Fellowship]</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>59:55.579</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6931981</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Mas</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Zachery Reinke</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>52.502</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>01:00:48.081</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>52.502</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4148536</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Vet</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Corey K</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>02:07.232</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>01:02:02.811</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>02:07.232</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pen</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>total_time</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>time_offset</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>racers</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>time1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>racers1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>58:06.300</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>58:06.300</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>02:47:28.983</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>02:47:28.983</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>59:55.579</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>59:55.579</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>zwift_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>pen</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Total Points</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>races</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Richmond Sprint</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Richmond Sprint 2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Richmond Sprint points</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Richmond Sprint 2 points</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>time_offset</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7965630</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Dexter Nguyen [Fellowship]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>20.582</v>
+      </c>
+      <c r="I2" t="n">
+        <v>27.567</v>
+      </c>
+      <c r="J2" t="n">
+        <v>30</v>
+      </c>
+      <c r="K2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8029063</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Marlon Garcia</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>19.575</v>
+      </c>
+      <c r="I3" t="n">
+        <v>26.189</v>
+      </c>
+      <c r="J3" t="n">
+        <v>30</v>
+      </c>
+      <c r="K3" t="n">
+        <v>30</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8311695</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Kyle Mueller (Fellowship)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>45</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>20.622</v>
+      </c>
+      <c r="I4" t="n">
+        <v>27.967</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K4" t="n">
+        <v>25</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8076817</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Ben Fryett (Fellowship)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>40</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>21.135</v>
+      </c>
+      <c r="I5" t="n">
+        <v>28.131</v>
+      </c>
+      <c r="J5" t="n">
+        <v>18</v>
+      </c>
+      <c r="K5" t="n">
+        <v>22</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8205262</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Seung-ah Lee&amp;#129430;</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>19.833</v>
+      </c>
+      <c r="I6" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="J6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K6" t="n">
+        <v>13</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1039349</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Joey Austerman</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>36</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>20.183</v>
+      </c>
+      <c r="I7" t="n">
+        <v>28.433</v>
+      </c>
+      <c r="J7" t="n">
+        <v>22</v>
+      </c>
+      <c r="K7" t="n">
+        <v>14</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6683427</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Evan Davis [Fellowship]</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>33</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>22.067</v>
+      </c>
+      <c r="I8" t="n">
+        <v>28.154</v>
+      </c>
+      <c r="J8" t="n">
+        <v>13</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8344285</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Wayne Giles</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>32</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>21.265</v>
+      </c>
+      <c r="I9" t="n">
+        <v>28.412</v>
+      </c>
+      <c r="J9" t="n">
+        <v>16</v>
+      </c>
+      <c r="K9" t="n">
+        <v>16</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8145883</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matthew Carter (Fellowship) </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>32</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>21.984</v>
+      </c>
+      <c r="I10" t="n">
+        <v>28.311</v>
+      </c>
+      <c r="J10" t="n">
+        <v>14</v>
+      </c>
+      <c r="K10" t="n">
+        <v>18</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>4148536</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Corey K</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>60</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>22.558</v>
+      </c>
+      <c r="I11" t="n">
+        <v>27.481</v>
+      </c>
+      <c r="J11" t="n">
+        <v>30</v>
+      </c>
+      <c r="K11" t="n">
+        <v>30</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6931981</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Zachery Reinke</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>50</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>22.582</v>
+      </c>
+      <c r="I12" t="n">
+        <v>28.599</v>
+      </c>
+      <c r="J12" t="n">
+        <v>25</v>
+      </c>
+      <c r="K12" t="n">
+        <v>25</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7742231</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Carter Costner [Fellowship]</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>44</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="I13" t="n">
+        <v>29.058</v>
+      </c>
+      <c r="J13" t="n">
+        <v>22</v>
+      </c>
+      <c r="K13" t="n">
+        <v>22</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>zwift_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>pen</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Total Points</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>races</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>time_offset</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7965630</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Dexter Nguyen [Fellowship]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8205262</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Seung-ah Lee&amp;#129430;</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8076817</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ben Fryett (Fellowship)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8311695</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Kyle Mueller (Fellowship)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1039349</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Joey Austerman</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8029063</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Marlon Garcia</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8344285</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Wayne Giles</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6683427</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Evan Davis [Fellowship]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8145883</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matthew Carter (Fellowship) </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7742231</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Carter Costner [Fellowship]</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6931981</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Zachery Reinke</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4148536</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Corey K</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pen</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>zwift_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>time1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>race_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>7965630</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Dexter Nguyen [Fellowship]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Mas</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>58:06.300</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>5752680</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>8205262</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Seung-ah Lee&amp;#129430;</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Jnr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>55:30.722</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>5752680</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>8076817</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ben Fryett (Fellowship)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mas</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>55:48.842</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>5752680</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>8311695</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Kyle Mueller (Fellowship)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mas</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>56:09.419</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5752680</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1039349</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Joey Austerman</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>60+</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>56:24.467</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>5752680</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>8029063</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Marlon Garcia</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mas</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>56:39.612</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5752680</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>8344285</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Wayne Giles</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vet</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>56:42.739</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5752680</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>6683427</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Evan Davis [Fellowship]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mas</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>58:35.367</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>5752680</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>8145883</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matthew Carter (Fellowship) </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vet</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>59:17.908</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5752680</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>7742231</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Carter Costner [Fellowship]</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Snr</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>59:55.579</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>5752680</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>6931981</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Zachery Reinke</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mas</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>01:00:48.081</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>5752680</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4148536</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Corey K</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vet</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>01:02:02.811</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>5752680</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/FellowshipChampionships/FellowshipChampionships.xlsx
+++ b/FellowshipChampionships/FellowshipChampionships.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1046,6 +1046,54 @@
         </is>
       </c>
       <c r="J13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>321711</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Jay Jensen (RtB)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>RtB</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>01:11:46.211</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1073,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1750,6 +1798,59 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>02:07.232</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>321711</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Jay Jensen (RtB)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>RtB</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>01:11:46.211</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>00.000</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1900,6 +2001,39 @@
         </is>
       </c>
       <c r="G4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>RtB</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>01:11:46.211</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>01:11:46.211</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1914,7 +2048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2490,6 +2624,50 @@
         <v>22</v>
       </c>
       <c r="L13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>321711</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Jay Jensen (RtB)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RtB</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>60</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>21.334</v>
+      </c>
+      <c r="I14" t="n">
+        <v>28.538</v>
+      </c>
+      <c r="J14" t="n">
+        <v>30</v>
+      </c>
+      <c r="K14" t="n">
+        <v>30</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2502,7 +2680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2914,6 +3092,38 @@
         <v>1</v>
       </c>
       <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>321711</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Jay Jensen (RtB)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RtB</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2926,7 +3136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3473,6 +3683,49 @@
         </is>
       </c>
       <c r="I13" t="n">
+        <v>5752680</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>321711</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Jay Jensen (RtB)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RtB</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>01:11:46.211</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>5752680</v>
       </c>
     </row>
